--- a/transactions/Recap_transaction_fonciere_FREEHOLD_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_FREEHOLD_appel_de_fonds.xlsx
@@ -178,12 +178,12 @@
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
-        <t>Forfait plancher : si le pourcentage donne moins de 10 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
+        <t>Forfait plancher : si le pourcentage donne moins de 20 000 000 IDR, ce forfait s'applique a la place du pourcentage.</t>
       </text>
     </comment>
     <comment ref="D27" authorId="0" shapeId="0">
       <text>
-        <t>MAX entre le pourcentage d'honoraires et le forfait minimum : si le pourcentage donne moins de 10 000 000 IDR, c'est le forfait qui s'applique.
+        <t>MAX entre le pourcentage d'honoraires et le forfait minimum : si le pourcentage donne moins de 20 000 000 IDR, c'est le forfait qui s'applique.
 La colonne des taux affiche le taux reellement supporte.</t>
       </text>
     </comment>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>10000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="16">
@@ -753,7 +753,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client, minimum 10 000 000 IDR)</t>
+          <t>Honoraires du notaire (1% du prix client, minimum 20 000 000 IDR)</t>
         </is>
       </c>
       <c r="C27" s="5">
@@ -919,7 +919,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 10 000 000 IDR (B15), auquel cas le forfait est retenu (formule MAX en D27).</t>
+          <t>Honoraires du notaire : le pourcentage s'applique sauf s'il donne moins que le forfait minimum de 20 000 000 IDR (B15), auquel cas le forfait est retenu (formule MAX en D27).</t>
         </is>
       </c>
     </row>

--- a/transactions/Recap_transaction_fonciere_FREEHOLD_appel_de_fonds.xlsx
+++ b/transactions/Recap_transaction_fonciere_FREEHOLD_appel_de_fonds.xlsx
@@ -734,7 +734,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Taxes gouvernementales (5% du prix client)</t>
+          <t>Taxes gouvernementales (5% du prix officiel)</t>
         </is>
       </c>
       <c r="C26" s="5">
@@ -742,7 +742,7 @@
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>D22*$B$13</f>
+        <f>D21*$B$13</f>
         <v/>
       </c>
       <c r="E26" s="3">
@@ -753,15 +753,15 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (1% du prix client, minimum 20 000 000 IDR)</t>
+          <t>Honoraires du notaire (1% du prix officiel, minimum 20 000 000 IDR)</t>
         </is>
       </c>
       <c r="C27" s="5">
-        <f>IF(D22=0,0,D27/D22)</f>
+        <f>IF(D21=0,0,D27/D21)</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>MAX(D22*$B$14,$B$15)</f>
+        <f>MAX(D21*$B$14,$B$15)</f>
         <v/>
       </c>
       <c r="E27" s="3">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>IF(D22=0,0,D28/D22)</f>
+        <f>IF(D21=0,0,D28/D21)</f>
         <v/>
       </c>
       <c r="D28" s="4">
@@ -926,7 +926,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Ces taux sont appliques au prix client avec commission. Remplacer D22 par D21 dans les formules de frais si la base retenue est le prix vendeur.</t>
+          <t>Les frais de notaire portent sur le PRIX OFFICIEL, c'est-a-dire le prix vendeur declare a l'acte (ligne 21), et non sur le prix client commission comprise.</t>
         </is>
       </c>
     </row>
